--- a/artfynd/A 42363-2024 artfynd.xlsx
+++ b/artfynd/A 42363-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120184895</v>
+        <v>120178293</v>
       </c>
       <c r="B2" t="n">
-        <v>91863</v>
+        <v>91884</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>798451</v>
+        <v>798550</v>
       </c>
       <c r="R2" t="n">
-        <v>7141111</v>
+        <v>7141055</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120184847</v>
+        <v>120178668</v>
       </c>
       <c r="B3" t="n">
-        <v>91884</v>
+        <v>91863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>798436</v>
+        <v>798523</v>
       </c>
       <c r="R3" t="n">
-        <v>7141118</v>
+        <v>7141063</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120178293</v>
+        <v>120178326</v>
       </c>
       <c r="B4" t="n">
-        <v>91884</v>
+        <v>91863</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>798550</v>
+        <v>798531</v>
       </c>
       <c r="R4" t="n">
-        <v>7141055</v>
+        <v>7141063</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120185288</v>
+        <v>120181112</v>
       </c>
       <c r="B5" t="n">
-        <v>90527</v>
+        <v>91254</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,37 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skäran, Skäran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>798480</v>
+        <v>798565</v>
       </c>
       <c r="R5" t="n">
-        <v>7141068</v>
+        <v>7141201</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,7 +1105,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1127,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120178668</v>
+        <v>120181636</v>
       </c>
       <c r="B6" t="n">
-        <v>91863</v>
+        <v>90527</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>798523</v>
+        <v>798539</v>
       </c>
       <c r="R6" t="n">
-        <v>7141063</v>
+        <v>7141215</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120184794</v>
+        <v>120184895</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>798433</v>
+        <v>798451</v>
       </c>
       <c r="R7" t="n">
-        <v>7141130</v>
+        <v>7141111</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120178326</v>
+        <v>120184847</v>
       </c>
       <c r="B8" t="n">
-        <v>91863</v>
+        <v>91884</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>798531</v>
+        <v>798436</v>
       </c>
       <c r="R8" t="n">
-        <v>7141063</v>
+        <v>7141118</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120181112</v>
+        <v>120185288</v>
       </c>
       <c r="B9" t="n">
-        <v>91254</v>
+        <v>90527</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,34 +1475,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skäran, Skäran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>798565</v>
+        <v>798480</v>
       </c>
       <c r="R9" t="n">
-        <v>7141201</v>
+        <v>7141068</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,6 +1556,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120181636</v>
+        <v>120184794</v>
       </c>
       <c r="B10" t="n">
-        <v>90527</v>
+        <v>91840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,21 +1591,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>798539</v>
+        <v>798433</v>
       </c>
       <c r="R10" t="n">
-        <v>7141215</v>
+        <v>7141130</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 42363-2024 artfynd.xlsx
+++ b/artfynd/A 42363-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120178293</v>
+        <v>120185288</v>
       </c>
       <c r="B2" t="n">
-        <v>91884</v>
+        <v>90545</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skäran, Skäran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>798550</v>
+        <v>798480</v>
       </c>
       <c r="R2" t="n">
-        <v>7141055</v>
+        <v>7141068</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120178668</v>
+        <v>120178293</v>
       </c>
       <c r="B3" t="n">
-        <v>91863</v>
+        <v>91902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>798523</v>
+        <v>798550</v>
       </c>
       <c r="R3" t="n">
-        <v>7141063</v>
+        <v>7141055</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120178326</v>
+        <v>120184794</v>
       </c>
       <c r="B4" t="n">
-        <v>91863</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>798531</v>
+        <v>798433</v>
       </c>
       <c r="R4" t="n">
-        <v>7141063</v>
+        <v>7141130</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1018,7 @@
         <v>120181112</v>
       </c>
       <c r="B5" t="n">
-        <v>91254</v>
+        <v>91272</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1123,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120181636</v>
+        <v>120178668</v>
       </c>
       <c r="B6" t="n">
-        <v>90527</v>
+        <v>91881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1139,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>798539</v>
+        <v>798523</v>
       </c>
       <c r="R6" t="n">
-        <v>7141215</v>
+        <v>7141063</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,7 +1242,7 @@
         <v>120184895</v>
       </c>
       <c r="B7" t="n">
-        <v>91863</v>
+        <v>91881</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1347,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120184847</v>
+        <v>120178326</v>
       </c>
       <c r="B8" t="n">
-        <v>91884</v>
+        <v>91881</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1367,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>798436</v>
+        <v>798531</v>
       </c>
       <c r="R8" t="n">
-        <v>7141118</v>
+        <v>7141063</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120185288</v>
+        <v>120181636</v>
       </c>
       <c r="B9" t="n">
-        <v>90527</v>
+        <v>90545</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,19 +1497,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skäran, Skäran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>798480</v>
+        <v>798539</v>
       </c>
       <c r="R9" t="n">
-        <v>7141068</v>
+        <v>7141215</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,7 +1557,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120184794</v>
+        <v>120184847</v>
       </c>
       <c r="B10" t="n">
-        <v>91840</v>
+        <v>91902</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,25 +1587,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>798433</v>
+        <v>798436</v>
       </c>
       <c r="R10" t="n">
-        <v>7141130</v>
+        <v>7141118</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 42363-2024 artfynd.xlsx
+++ b/artfynd/A 42363-2024 artfynd.xlsx
@@ -1463,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120181636</v>
+        <v>120184847</v>
       </c>
       <c r="B9" t="n">
-        <v>90545</v>
+        <v>91902</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,25 +1475,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>798539</v>
+        <v>798436</v>
       </c>
       <c r="R9" t="n">
-        <v>7141215</v>
+        <v>7141118</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120184847</v>
+        <v>120181636</v>
       </c>
       <c r="B10" t="n">
-        <v>91902</v>
+        <v>90545</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,25 +1587,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>798436</v>
+        <v>798539</v>
       </c>
       <c r="R10" t="n">
-        <v>7141118</v>
+        <v>7141215</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 42363-2024 artfynd.xlsx
+++ b/artfynd/A 42363-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120185288</v>
+        <v>120184794</v>
       </c>
       <c r="B2" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skäran, Skäran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>798480</v>
+        <v>798433</v>
       </c>
       <c r="R2" t="n">
-        <v>7141068</v>
+        <v>7141130</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120184794</v>
+        <v>120181112</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>91272</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>798433</v>
+        <v>798565</v>
       </c>
       <c r="R4" t="n">
-        <v>7141130</v>
+        <v>7141201</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120181112</v>
+        <v>120184895</v>
       </c>
       <c r="B5" t="n">
-        <v>91272</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>798565</v>
+        <v>798451</v>
       </c>
       <c r="R5" t="n">
-        <v>7141201</v>
+        <v>7141111</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120178668</v>
+        <v>120184847</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>91902</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>798523</v>
+        <v>798436</v>
       </c>
       <c r="R6" t="n">
-        <v>7141063</v>
+        <v>7141118</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120184895</v>
+        <v>120185288</v>
       </c>
       <c r="B7" t="n">
-        <v>91881</v>
+        <v>90545</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,38 +1247,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skäran, Skäran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>798451</v>
+        <v>798480</v>
       </c>
       <c r="R7" t="n">
-        <v>7141111</v>
+        <v>7141068</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1313,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1323,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,6 +1332,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120178326</v>
+        <v>120181636</v>
       </c>
       <c r="B8" t="n">
-        <v>91881</v>
+        <v>90545</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,25 +1363,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>798531</v>
+        <v>798539</v>
       </c>
       <c r="R8" t="n">
-        <v>7141063</v>
+        <v>7141215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120184847</v>
+        <v>120178668</v>
       </c>
       <c r="B9" t="n">
-        <v>91902</v>
+        <v>91881</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,21 +1479,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>798436</v>
+        <v>798523</v>
       </c>
       <c r="R9" t="n">
-        <v>7141118</v>
+        <v>7141063</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120181636</v>
+        <v>120178326</v>
       </c>
       <c r="B10" t="n">
-        <v>90545</v>
+        <v>91881</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,25 +1587,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>798539</v>
+        <v>798531</v>
       </c>
       <c r="R10" t="n">
-        <v>7141215</v>
+        <v>7141063</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 42363-2024 artfynd.xlsx
+++ b/artfynd/A 42363-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120184794</v>
+        <v>120185288</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skäran, Skäran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>798433</v>
+        <v>798480</v>
       </c>
       <c r="R2" t="n">
-        <v>7141130</v>
+        <v>7141068</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120178293</v>
+        <v>120184794</v>
       </c>
       <c r="B3" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>798550</v>
+        <v>798433</v>
       </c>
       <c r="R3" t="n">
-        <v>7141055</v>
+        <v>7141130</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1011,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120184895</v>
+        <v>120178326</v>
       </c>
       <c r="B5" t="n">
         <v>91881</v>
@@ -1051,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>798451</v>
+        <v>798531</v>
       </c>
       <c r="R5" t="n">
-        <v>7141111</v>
+        <v>7141063</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120184847</v>
+        <v>120184895</v>
       </c>
       <c r="B6" t="n">
-        <v>91902</v>
+        <v>91881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>798436</v>
+        <v>798451</v>
       </c>
       <c r="R6" t="n">
-        <v>7141118</v>
+        <v>7141111</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120185288</v>
+        <v>120178668</v>
       </c>
       <c r="B7" t="n">
-        <v>90545</v>
+        <v>91881</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,41 +1251,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skäran, Skäran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>798480</v>
+        <v>798523</v>
       </c>
       <c r="R7" t="n">
-        <v>7141068</v>
+        <v>7141063</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1323,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,7 +1333,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120181636</v>
+        <v>120184847</v>
       </c>
       <c r="B8" t="n">
-        <v>90545</v>
+        <v>91902</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,25 +1363,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>798539</v>
+        <v>798436</v>
       </c>
       <c r="R8" t="n">
-        <v>7141215</v>
+        <v>7141118</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120178668</v>
+        <v>120181636</v>
       </c>
       <c r="B9" t="n">
-        <v>91881</v>
+        <v>90545</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,25 +1475,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>798523</v>
+        <v>798539</v>
       </c>
       <c r="R9" t="n">
-        <v>7141063</v>
+        <v>7141215</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120178326</v>
+        <v>120178293</v>
       </c>
       <c r="B10" t="n">
-        <v>91881</v>
+        <v>91902</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,21 +1591,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>798531</v>
+        <v>798550</v>
       </c>
       <c r="R10" t="n">
-        <v>7141063</v>
+        <v>7141055</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 42363-2024 artfynd.xlsx
+++ b/artfynd/A 42363-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120185288</v>
+        <v>120181112</v>
       </c>
       <c r="B2" t="n">
-        <v>90545</v>
+        <v>91272</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skäran, Skäran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>798480</v>
+        <v>798565</v>
       </c>
       <c r="R2" t="n">
-        <v>7141068</v>
+        <v>7141201</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120184794</v>
+        <v>120184847</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>798433</v>
+        <v>798436</v>
       </c>
       <c r="R3" t="n">
-        <v>7141130</v>
+        <v>7141118</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120181112</v>
+        <v>120178293</v>
       </c>
       <c r="B4" t="n">
-        <v>91272</v>
+        <v>91902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>798565</v>
+        <v>798550</v>
       </c>
       <c r="R4" t="n">
-        <v>7141201</v>
+        <v>7141055</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120178326</v>
+        <v>120184895</v>
       </c>
       <c r="B5" t="n">
         <v>91881</v>
@@ -1055,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>798531</v>
+        <v>798451</v>
       </c>
       <c r="R5" t="n">
-        <v>7141063</v>
+        <v>7141111</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120184895</v>
+        <v>120184794</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>798451</v>
+        <v>798433</v>
       </c>
       <c r="R6" t="n">
-        <v>7141111</v>
+        <v>7141130</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120178668</v>
+        <v>120178326</v>
       </c>
       <c r="B7" t="n">
         <v>91881</v>
@@ -1279,7 +1275,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>798523</v>
+        <v>798531</v>
       </c>
       <c r="R7" t="n">
         <v>7141063</v>
@@ -1314,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120184847</v>
+        <v>120181636</v>
       </c>
       <c r="B8" t="n">
-        <v>91902</v>
+        <v>90545</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>798436</v>
+        <v>798539</v>
       </c>
       <c r="R8" t="n">
-        <v>7141118</v>
+        <v>7141215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120181636</v>
+        <v>120178668</v>
       </c>
       <c r="B9" t="n">
-        <v>90545</v>
+        <v>91881</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>798539</v>
+        <v>798523</v>
       </c>
       <c r="R9" t="n">
-        <v>7141215</v>
+        <v>7141063</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120178293</v>
+        <v>120185288</v>
       </c>
       <c r="B10" t="n">
-        <v>91902</v>
+        <v>90545</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,38 +1583,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skäran, Skäran, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>798550</v>
+        <v>798480</v>
       </c>
       <c r="R10" t="n">
-        <v>7141055</v>
+        <v>7141068</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1669,6 +1668,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42363-2024 artfynd.xlsx
+++ b/artfynd/A 42363-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120181112</v>
+        <v>120184895</v>
       </c>
       <c r="B2" t="n">
-        <v>91272</v>
+        <v>91881</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>798565</v>
+        <v>798451</v>
       </c>
       <c r="R2" t="n">
-        <v>7141201</v>
+        <v>7141111</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120178293</v>
+        <v>120178326</v>
       </c>
       <c r="B4" t="n">
-        <v>91902</v>
+        <v>91881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>798550</v>
+        <v>798531</v>
       </c>
       <c r="R4" t="n">
-        <v>7141055</v>
+        <v>7141063</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120184895</v>
+        <v>120178668</v>
       </c>
       <c r="B5" t="n">
         <v>91881</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>798451</v>
+        <v>798523</v>
       </c>
       <c r="R5" t="n">
-        <v>7141111</v>
+        <v>7141063</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120178326</v>
+        <v>120181636</v>
       </c>
       <c r="B7" t="n">
-        <v>91881</v>
+        <v>90545</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>798531</v>
+        <v>798539</v>
       </c>
       <c r="R7" t="n">
-        <v>7141063</v>
+        <v>7141215</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120181636</v>
+        <v>120178293</v>
       </c>
       <c r="B8" t="n">
-        <v>90545</v>
+        <v>91902</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>798539</v>
+        <v>798550</v>
       </c>
       <c r="R8" t="n">
-        <v>7141215</v>
+        <v>7141055</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120178668</v>
+        <v>120185288</v>
       </c>
       <c r="B9" t="n">
-        <v>91881</v>
+        <v>90545</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,38 +1471,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skäran, Skäran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>798523</v>
+        <v>798480</v>
       </c>
       <c r="R9" t="n">
-        <v>7141063</v>
+        <v>7141068</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,6 +1556,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1571,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120185288</v>
+        <v>120181112</v>
       </c>
       <c r="B10" t="n">
-        <v>90545</v>
+        <v>91272</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,37 +1591,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skäran, Skäran, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>798480</v>
+        <v>798565</v>
       </c>
       <c r="R10" t="n">
-        <v>7141068</v>
+        <v>7141201</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,7 +1669,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42363-2024 artfynd.xlsx
+++ b/artfynd/A 42363-2024 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120178668</v>
+        <v>120184794</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>798523</v>
+        <v>798433</v>
       </c>
       <c r="R5" t="n">
-        <v>7141063</v>
+        <v>7141130</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120184794</v>
+        <v>120178668</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>798433</v>
+        <v>798523</v>
       </c>
       <c r="R6" t="n">
-        <v>7141130</v>
+        <v>7141063</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 42363-2024 artfynd.xlsx
+++ b/artfynd/A 42363-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120184895</v>
+        <v>120178668</v>
       </c>
       <c r="B2" t="n">
         <v>91881</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>798451</v>
+        <v>798523</v>
       </c>
       <c r="R2" t="n">
-        <v>7141111</v>
+        <v>7141063</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120184847</v>
+        <v>120181636</v>
       </c>
       <c r="B3" t="n">
-        <v>91902</v>
+        <v>90545</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>798436</v>
+        <v>798539</v>
       </c>
       <c r="R3" t="n">
-        <v>7141118</v>
+        <v>7141215</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120178326</v>
+        <v>120178293</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>91902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>798531</v>
+        <v>798550</v>
       </c>
       <c r="R4" t="n">
-        <v>7141063</v>
+        <v>7141055</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120184794</v>
+        <v>120178326</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>798433</v>
+        <v>798531</v>
       </c>
       <c r="R5" t="n">
-        <v>7141130</v>
+        <v>7141063</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120178668</v>
+        <v>120181112</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>91272</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>798523</v>
+        <v>798565</v>
       </c>
       <c r="R6" t="n">
-        <v>7141063</v>
+        <v>7141201</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120181636</v>
+        <v>120184847</v>
       </c>
       <c r="B7" t="n">
-        <v>90545</v>
+        <v>91902</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>5449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>798539</v>
+        <v>798436</v>
       </c>
       <c r="R7" t="n">
-        <v>7141215</v>
+        <v>7141118</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120178293</v>
+        <v>120185288</v>
       </c>
       <c r="B8" t="n">
-        <v>91902</v>
+        <v>90545</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,38 +1359,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skäran, Skäran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>798550</v>
+        <v>798480</v>
       </c>
       <c r="R8" t="n">
-        <v>7141055</v>
+        <v>7141068</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1425,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1435,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,6 +1444,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1459,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120185288</v>
+        <v>120184895</v>
       </c>
       <c r="B9" t="n">
-        <v>90545</v>
+        <v>91881</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,41 +1475,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skäran, Skäran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>798480</v>
+        <v>798451</v>
       </c>
       <c r="R9" t="n">
-        <v>7141068</v>
+        <v>7141111</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,7 +1557,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120181112</v>
+        <v>120184794</v>
       </c>
       <c r="B10" t="n">
-        <v>91272</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,21 +1591,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>798565</v>
+        <v>798433</v>
       </c>
       <c r="R10" t="n">
-        <v>7141201</v>
+        <v>7141130</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 42363-2024 artfynd.xlsx
+++ b/artfynd/A 42363-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120178668</v>
+        <v>120181112</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>91272</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>798523</v>
+        <v>798565</v>
       </c>
       <c r="R2" t="n">
-        <v>7141063</v>
+        <v>7141201</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120181636</v>
+        <v>120184794</v>
       </c>
       <c r="B3" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>798539</v>
+        <v>798433</v>
       </c>
       <c r="R3" t="n">
-        <v>7141215</v>
+        <v>7141130</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120178293</v>
+        <v>120184847</v>
       </c>
       <c r="B4" t="n">
         <v>91902</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>798550</v>
+        <v>798436</v>
       </c>
       <c r="R4" t="n">
-        <v>7141055</v>
+        <v>7141118</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120181112</v>
+        <v>120178293</v>
       </c>
       <c r="B6" t="n">
-        <v>91272</v>
+        <v>91902</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>798565</v>
+        <v>798550</v>
       </c>
       <c r="R6" t="n">
-        <v>7141201</v>
+        <v>7141055</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120184847</v>
+        <v>120178668</v>
       </c>
       <c r="B7" t="n">
-        <v>91902</v>
+        <v>91881</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>798436</v>
+        <v>798523</v>
       </c>
       <c r="R7" t="n">
-        <v>7141118</v>
+        <v>7141063</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120185288</v>
+        <v>120181636</v>
       </c>
       <c r="B8" t="n">
         <v>90545</v>
@@ -1381,19 +1381,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skäran, Skäran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>798480</v>
+        <v>798539</v>
       </c>
       <c r="R8" t="n">
-        <v>7141068</v>
+        <v>7141215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,7 +1441,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1463,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120184895</v>
+        <v>120185288</v>
       </c>
       <c r="B9" t="n">
-        <v>91881</v>
+        <v>90545</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,38 +1471,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skäran, Skäran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>798451</v>
+        <v>798480</v>
       </c>
       <c r="R9" t="n">
-        <v>7141111</v>
+        <v>7141068</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,6 +1556,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120184794</v>
+        <v>120184895</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,25 +1587,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>798433</v>
+        <v>798451</v>
       </c>
       <c r="R10" t="n">
-        <v>7141130</v>
+        <v>7141111</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
